--- a/products-storage/10-avans-usloviya-i-pribyl/09-raschet-otrabotannoy-chasti-avansa.xlsx
+++ b/products-storage/10-avans-usloviya-i-pribyl/09-raschet-otrabotannoy-chasti-avansa.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -597,10 +597,10 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="65" customHeight="1">
+    <row r="4" ht="104" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>От вас требуют вернуть аванс. В требовании почти всегда стоит вся полученная сумма — так его пишут по умолчанию, независимо от того, сколько работ вы успели выполнить. Возврату подлежит разница между полученным авансом и тем, что этим авансом уже закрыто. Разницу считаете вы: объём выполненного доказывает подрядчик, и пока цифры нет на бумаге, ваше письмо остаётся просьбой войти в положение.</t>
+          <t>От вас требуют вернуть аванс. В требовании почти всегда стоит вся полученная сумма — так его пишут по умолчанию, независимо от того, сколько работ вы успели выполнить. Возврату подлежит разница между полученным авансом и тем, что этим авансом уже закрыто. Разницу считаете вы, и это не фигура речи: перечисление аванса доказывает тот, кто требует его назад, а то, что аванс отработан, — подрядчик. Так распределяется бремя доказывания по устоявшейся практике (процессуальное правило — статья 65 Арбитражного процессуального кодекса РФ, а не норма о подряде); как оно ляжет в вашем деле, оценивает юрист. Пока цифры нет на бумаге, ваше письмо остаётся просьбой войти в положение.</t>
         </is>
       </c>
     </row>
@@ -716,8 +716,15 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="39" customHeight="1">
+    <row r="21" ht="78" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Две оговорки, из-за которых эти статьи читают не глядя и ошибаются. Первая: статья 717 начинается словами «если иное не предусмотрено договором подряда» — договор может установить свой порядок, и в договорах субподряда это «иное» встречается постоянно. Сначала смотрите свой договор, потом кодекс. Вторая: статьи 715 и 717 — общие правила о подряде, к строительному подряду они применяются, пока правила о нём не устанавливают другого; статья 753 — правило именно строительного подряда. Какая норма работает в вашем случае, определяет юрист.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="39" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Ни одного срока и ни одной ставки числом в файле нет намеренно. Срок ответа на требование берётся из вашего договора, сроки исковой давности и порядок их исчисления — вопрос к юристу на дату обращения. Скачанный файл не обновляется, а зашитое в нём число выглядит проверенным.</t>
         </is>

--- a/products-storage/10-avans-usloviya-i-pribyl/09-raschet-otrabotannoy-chasti-avansa.xlsx
+++ b/products-storage/10-avans-usloviya-i-pribyl/09-raschet-otrabotannoy-chasti-avansa.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -597,134 +597,141 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="104" customHeight="1">
+    <row r="4" ht="65" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>От вас требуют вернуть аванс. В требовании почти всегда стоит вся полученная сумма — так его пишут по умолчанию, независимо от того, сколько работ вы успели выполнить. Возврату подлежит разница между полученным авансом и тем, что этим авансом уже закрыто. Разницу считаете вы, и это не фигура речи: перечисление аванса доказывает тот, кто требует его назад, а то, что аванс отработан, — подрядчик. Так распределяется бремя доказывания по устоявшейся практике (процессуальное правило — статья 65 Арбитражного процессуального кодекса РФ, а не норма о подряде); как оно ляжет в вашем деле, оценивает юрист. Пока цифры нет на бумаге, ваше письмо остаётся просьбой войти в положение.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="39" customHeight="1">
+          <t>От вас требуют вернуть аванс. В требовании почти всегда стоит вся полученная сумма — так его пишут по умолчанию, независимо от того, сколько работ вы успели выполнить. Предмет разговора — разница между этой суммой и тем, что подтверждено вашими документами. Какая часть аванса подлежит возврату именно в вашем случае, зависит от договора и от основания прекращения и оценивается юристом; файл считает разницу и показывает, из чего она сложилась.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>Считаете её вы, и это не фигура речи: перечисление аванса доказывает тот, кто требует его назад, а то, что аванс отработан, — подрядчик. Так распределяется бремя доказывания по устоявшейся практике (процессуальное правило — статья 65 Арбитражного процессуального кодекса РФ, а не норма о подряде); как оно ляжет в вашем деле, оценивает юрист. Пока цифры нет на бумаге, ваше письмо остаётся просьбой войти в положение.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="39" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
           <t>Файл собирает эту цифру из документов, которые у вас уже есть, и показывает, из чего она сложилась. Ровно этого расчёта не хватает в девяти обращениях к юристу из десяти, и именно на его составление уходят первые оплаченные часы.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Чего он не делает</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Не квалифицирует отношения сторон, не оценивает перспективу спора и не предсказывает, чем кончится дело. Не заменяет юриста и не является юридической консультацией. Основание прекращения договора вы вводите как факт из документов, а не как правовую позицию: какие последствия оно влечёт, оценивает юрист по вашему договору и вашей переписке.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Не считает проценты, неустойку и убытки. Это отдельные требования со своими основаниями, и в сальдо расчётов они не входят.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Порядок работы</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>1. Лист «Договор и аванс» — реквизиты, сумма договора, сколько аванса получено по платёжным поручениям, что и когда от вас потребовали.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="39" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2. Лист «Выполнено» — все акты по объекту, включая те, которые вторая сторона не подписала. Неподписанный акт вносится наравне с подписанным: он не даёт бесспорной суммы, но и молчать о нём нельзя.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="39" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>2. Лист «Выполнено» — все акты по объекту, включая те, которые вторая сторона не подписала. Неподписанный акт вносится наравне с подписанным: он не даёт бесспорной суммы, но и молчать о нём нельзя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>3. Лист «Встречное» — материалы, затраты и удержанное гарантийное. Акты сюда не переносятся: они уже посчитаны на листе «Выполнено», а одна и та же сумма, попавшая в расчёт дважды, обесценивает весь расчёт целиком.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>4. Лист «Сальдо» — итог и блок проверок. Начинайте чтение с проверок: если там есть красная строка, итог считать рано.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>5. Лист «Акт сверки» — печатная форма из тех же чисел. Ни одно число в неё не вводится руками.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Цвета</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="39" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17" ht="39" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Синим — то, что вводите вы. Чёрным — то, что считает файл. Зелёным — ссылка на другой лист. Жёлтая заливка означает поле ввода: если вы пишете поверх формулы, расчёт молча перестаёт быть расчётом.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Что нельзя делать до того, как расчёт готов</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Не подписывать акт сверки со стороны генподрядчика, не подписывать соглашение о зачёте, не признавать сумму в переписке — ни цифрой, ни словами «мы вернём, дайте срок». Своя цифра должна появиться раньше ответа на чужую. Какое значение подписанный вами документ будет иметь в вашем деле — оценивает юрист, и оценивает уже по факту.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Про статьи</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="78" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Судьбу неотработанной части при расторжении договора обсуждают вокруг статьи 453 Гражданского кодекса РФ о последствиях расторжения и главы 60 того же кодекса о неосновательном обогащении; последствия отказа заказчика от исполнения договора подряда — вокруг статьи 717, отказа из-за нарушений подрядчика — вокруг статьи 715; значение акта, от подписания которого сторона уклонилась, — вокруг пункта 4 статьи 753. Здесь названо, вокруг чего идёт разговор, а не то, чем он кончится: применимость каждой из них к вашему случаю определяет юрист.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="78" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>Судьбу неотработанной части при расторжении договора обсуждают вокруг статьи 453 Гражданского кодекса РФ о последствиях расторжения и главы 60 того же кодекса о неосновательном обогащении; последствия отказа заказчика от исполнения договора подряда — вокруг статьи 717, отказа из-за нарушений подрядчика — вокруг статьи 715; значение акта, от подписания которого сторона уклонилась, — вокруг пункта 4 статьи 753. Здесь названо, вокруг чего идёт разговор, а не то, чем он кончится: применимость каждой из них к вашему случаю определяет юрист.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="78" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>Две оговорки, из-за которых эти статьи читают не глядя и ошибаются. Первая: статья 717 начинается словами «если иное не предусмотрено договором подряда» — договор может установить свой порядок, и в договорах субподряда это «иное» встречается постоянно. Сначала смотрите свой договор, потом кодекс. Вторая: статьи 715 и 717 — общие правила о подряде, к строительному подряду они применяются, пока правила о нём не устанавливают другого; статья 753 — правило именно строительного подряда. Какая норма работает в вашем случае, определяет юрист.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="39" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23" ht="39" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Ни одного срока и ни одной ставки числом в файле нет намеренно. Срок ответа на требование берётся из вашего договора, сроки исковой давности и порядок их исчисления — вопрос к юристу на дату обращения. Скачанный файл не обновляется, а зашитое в нём число выглядит проверенным.</t>
         </is>
@@ -732,12 +739,12 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6"/>
-    <mergeCell ref="A17"/>
-    <mergeCell ref="A9"/>
+    <mergeCell ref="A18"/>
     <mergeCell ref="A3"/>
-    <mergeCell ref="A15"/>
-    <mergeCell ref="A19"/>
+    <mergeCell ref="A7"/>
+    <mergeCell ref="A20"/>
+    <mergeCell ref="A16"/>
+    <mergeCell ref="A10"/>
     <mergeCell ref="A1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -750,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -953,40 +960,47 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>генподрядчик отказался от исполнения</t>
+          <t>генподрядчик отказался от исполнения, о наших нарушениях не заявлено</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>генподрядчик расторг из-за нарушений с нашей стороны</t>
+          <t>генподрядчик отказался от исполнения, ссылаясь на наши нарушения</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>мы отказались от исполнения</t>
+          <t>договор расторгнут по решению суда</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>соглашение сторон</t>
+          <t>мы отказались от исполнения</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
+          <t>соглашение сторон</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
           <t>договор не расторгнут, требование заявлено</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Основание вводится как факт из документа. Оно влияет на то, какие встречные суммы вообще имеет смысл заявлять, но вывод об этом делает юрист: таблица подсказывает, а не решает.</t>
         </is>
@@ -994,15 +1008,15 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A15:C15"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Выберите основание из списка" type="list">
-      <formula1>=$A$22:$A$26</formula1>
+      <formula1>=$A$22:$A$27</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3539,7 +3553,7 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>генподрядчик отказался от исполнения</t>
+          <t>генподрядчик отказался от исполнения, о наших нарушениях не заявлено</t>
         </is>
       </c>
     </row>

--- a/products-storage/10-avans-usloviya-i-pribyl/09-raschet-otrabotannoy-chasti-avansa.xlsx
+++ b/products-storage/10-avans-usloviya-i-pribyl/09-raschet-otrabotannoy-chasti-avansa.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -614,7 +614,7 @@
     <row r="6" ht="39" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Файл собирает эту цифру из документов, которые у вас уже есть, и показывает, из чего она сложилась. Ровно этого расчёта не хватает в девяти обращениях к юристу из десяти, и именно на его составление уходят первые оплаченные часы.</t>
+          <t>Файл собирает эту цифру из документов, которые у вас уже есть, и показывает, из чего она сложилась. Именно этого расчёта обычно не хватает к первой встрече с юристом, и на его составление уходят первые оплаченные часы.</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
     <row r="12" ht="39" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2. Лист «Выполнено» — все акты по объекту, включая те, которые вторая сторона не подписала. Неподписанный акт вносится наравне с подписанным: он не даёт бесспорной суммы, но и молчать о нём нельзя.</t>
+          <t>2. Лист «Выполнено» — все акты по объекту, включая те, которые вторая сторона не подписала. Неподписанный акт вносится наравне с подписанным: суммы, подтверждённой обеими сторонами, он не даёт, но и молчать о нём нельзя.</t>
         </is>
       </c>
     </row>
@@ -712,33 +712,54 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>Про односторонний акт</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="65" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>В реестре «Выполнено» есть статус «подписан односторонне», и он не то же самое, что «передан, не подписан». Механизм даёт пункт 4 статьи 753 Гражданского кодекса РФ: сдача и приёмка оформляются актом, подписанным обеими сторонами, а при отказе одной из сторон от подписания в акте делается отметка об этом и акт подписывается другой стороной. Так и появляется односторонний акт — это не акт, на который просто не ответили, а акт с зафиксированным отказом, подписанный вами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="65" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Что это даёт в вашем деле, здесь не сказано намеренно. Тот же пункт говорит, что односторонний акт может быть признан судом недействительным, если мотивы отказа от подписания признаны обоснованными, — то есть вес такого акта зависит от содержания отказа, а это оценка, и делает её юрист. Поэтому на листе «Сальдо» односторонние акты стоят отдельной строкой от переданных без подписи: складывать в одну сумму то, что норма различает, значит потерять различие в самом начале.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>Про статьи</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="78" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="24" ht="78" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Судьбу неотработанной части при расторжении договора обсуждают вокруг статьи 453 Гражданского кодекса РФ о последствиях расторжения и главы 60 того же кодекса о неосновательном обогащении; последствия отказа заказчика от исполнения договора подряда — вокруг статьи 717, отказа из-за нарушений подрядчика — вокруг статьи 715; значение акта, от подписания которого сторона уклонилась, — вокруг пункта 4 статьи 753. Здесь названо, вокруг чего идёт разговор, а не то, чем он кончится: применимость каждой из них к вашему случаю определяет юрист.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="78" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="25" ht="78" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Две оговорки, из-за которых эти статьи читают не глядя и ошибаются. Первая: статья 717 начинается словами «если иное не предусмотрено договором подряда» — договор может установить свой порядок, и в договорах субподряда это «иное» встречается постоянно. Сначала смотрите свой договор, потом кодекс. Вторая: статьи 715 и 717 — общие правила о подряде, к строительному подряду они применяются, пока правила о нём не устанавливают другого; статья 753 — правило именно строительного подряда. Какая норма работает в вашем случае, определяет юрист.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="39" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="26" ht="39" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Ни одного срока и ни одной ставки числом в файле нет намеренно. Срок ответа на требование берётся из вашего договора, сроки исковой давности и порядок их исчисления — вопрос к юристу на дату обращения. Скачанный файл не обновляется, а зашитое в нём число выглядит проверенным.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A18"/>
     <mergeCell ref="A3"/>
     <mergeCell ref="A7"/>
@@ -746,6 +767,7 @@
     <mergeCell ref="A16"/>
     <mergeCell ref="A10"/>
     <mergeCell ref="A1"/>
+    <mergeCell ref="A23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -909,7 +931,7 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Неотработанный аванс по бесспорным документам</t>
+          <t>Аванс, не закрытый двусторонними актами</t>
         </is>
       </c>
       <c r="B17" s="8">
@@ -918,7 +940,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>аванс минус то, что закрыто подписанными актами. Это и есть сумма, о которой спорить не о чем; всё остальное — предмет обоснования</t>
+          <t>аванс минус то, что закрыто подписанными актами. Эта часть аванса не подтверждена двусторонними документами, и с неё начинается разговор; подлежит ли она возврату и в каком объёме — зависит от основания прекращения договора и от его условий</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1078,7 @@
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Неподписанный акт вносится наравне с подписанным. Бесспорной суммы он не даёт, но он показывает, что работы передавались, и без него расчёт выглядит так, будто вы ничего не сделали. Дата передачи и чем она подтверждена — здесь самые важные колонки: без них акт не считается переданным.</t>
+          <t>Неподписанный акт вносится наравне с подписанным. Суммы, подтверждённой обеими сторонами, он не даёт, но он показывает, что работы передавались, и без него расчёт выглядит так, будто вы ничего не сделали. Дата передачи и чем она подтверждена — здесь самые важные колонки: без них акт не считается переданным.</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2173,7 @@
     <row r="57" ht="60" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Колонка «Не оплачено» считается как стоимость акта минус зачтённое в счёт аванса минус оплаченное деньгами. По подписанным актам это задолженность генподрядчика перед вами, и она уменьшает сумму к возврату — но требованием о возврате аванса она не закрывается автоматически: зачёт встречных требований оформляется отдельно и не всегда допустим. Порядок оформления обсуждайте с юристом.</t>
+          <t>Колонка «Не оплачено» считается как стоимость акта минус зачтённое в счёт аванса минус оплаченное деньгами. По подписанным актам это задолженность генподрядчика перед вами, и она уменьшает сумму к возврату — но требованием о возврате аванса она не закрывается автоматически: зачёт встречных требований — самостоятельная сделка (для зачёта достаточно заявления одной стороны, статья 410 Гражданского кодекса РФ), и он допускается не во всех случаях (статья 411 того же кодекса). Порядок оформления обсуждайте с юристом.</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2733,7 @@
     <row r="40" ht="46" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Гарантийное удержание, уже удержанное генподрядчиком из оплаченных актов, вносится сюда: это ваши деньги, находящиеся у него, и в сальдо расчётов они на вашей стороне. Срок и событие его возврата берите из договора — может оказаться, что срок ещё не наступил, и тогда это надо назвать в письме прямо, а не умолчать.</t>
+          <t>Гарантийное удержание, уже удержанное генподрядчиком из оплаченных актов, вносится сюда: это удержанная им часть оплаты по вашим актам, и в сальдо расчётов она на вашей стороне. Чем именно является удержание по вашему договору — частью цены с отложенным сроком, обеспечением или чем-то ещё — определяет формулировка договора, и от неё же зависит, когда его возвращают. Срок и событие возврата берите из договора — может оказаться, что срок ещё не наступил, и тогда это надо назвать в письме прямо, а не умолчать.</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -2847,7 +2869,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>бесспорная часть выполненного</t>
+          <t>часть выполненного, подтверждённая обеими сторонами</t>
         </is>
       </c>
     </row>
@@ -2887,21 +2909,21 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>задолженность генподрядчика перед вами по бесспорным документам</t>
+          <t>задолженность генподрядчика перед вами по документам, подписанным обеими сторонами</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Бесспорная часть</t>
+          <t>Не закрытая актами часть</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>Неотработанный аванс по бесспорным документам</t>
+          <t>Аванс, не закрытый двусторонними актами</t>
         </is>
       </c>
       <c r="B17" s="23">
@@ -2910,7 +2932,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>аванс минус закрытое подписанными актами. Именно эту сумму, а не весь аванс, имеет смысл обсуждать как отправную точку</t>
+          <t>аванс минус закрытое подписанными актами. Именно эту сумму, а не весь аванс, имеет смысл обсуждать как отправную точку; подлежит ли она возврату целиком — отдельный вопрос</t>
         </is>
       </c>
     </row>
@@ -2924,11 +2946,11 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Работы переданы, акты не подписаны или подписаны односторонне</t>
+          <t>Работы переданы, акты не подписаны</t>
         </is>
       </c>
       <c r="B20" s="8">
-        <f>SUMIF('Выполнено'!F6:F45,"передан, не подписан",'Выполнено'!E6:E45)+SUMIF('Выполнено'!F6:F45,"подписан односторонне",'Выполнено'!E6:E45)</f>
+        <f>SUMIF('Выполнено'!F6:F45,"передан, не подписан",'Выполнено'!E6:E45)</f>
         <v/>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2940,271 +2962,287 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Материалы и оборудование</t>
+          <t>Работы переданы, акты подписаны односторонне</t>
         </is>
       </c>
       <c r="B21" s="8">
-        <f>SUMIF('Встречное'!B6:B30,"материалы переданы генподрядчику",'Встречное'!D6:D30)+SUMIF('Встречное'!B6:B30,"материалы и оборудование остались на объекте",'Встречное'!D6:D30)</f>
-        <v/>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
+        <f>SUMIF('Выполнено'!F6:F45,"подписан односторонне",'Выполнено'!E6:E45)</f>
+        <v/>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>отдельно от предыдущей строки: по пункту 4 статьи 753 ГК РФ это документы разного веса. Что даёт односторонний акт в вашем деле, оценивает юрист — см. лист «Как читать»</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Затраты на мобилизацию и демобилизацию</t>
+          <t>Материалы и оборудование</t>
         </is>
       </c>
       <c r="B22" s="8">
-        <f>SUMIF('Встречное'!B6:B30,"затраты на мобилизацию и демобилизацию",'Встречное'!D6:D30)</f>
-        <v/>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>самая спорная строка расчёта: зависит от основания прекращения договора, оценивает юрист</t>
-        </is>
-      </c>
+        <f>SUMIF('Встречное'!B6:B30,"материалы переданы генподрядчику",'Встречное'!D6:D30)+SUMIF('Встречное'!B6:B30,"материалы и оборудование остались на объекте",'Встречное'!D6:D30)</f>
+        <v/>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Гарантийное удержание из оплаченных актов</t>
+          <t>Затраты на мобилизацию и демобилизацию</t>
         </is>
       </c>
       <c r="B23" s="8">
-        <f>SUMIF('Встречное'!B6:B30,"гарантийное удержание из оплаченных актов",'Встречное'!D6:D30)</f>
+        <f>SUMIF('Встречное'!B6:B30,"затраты на мобилизацию и демобилизацию",'Встречное'!D6:D30)</f>
         <v/>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>ваши деньги у генподрядчика. Проверьте по договору, наступил ли срок возврата</t>
+          <t>самая спорная строка расчёта: зависит от основания прекращения договора, оценивает юрист</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Иное</t>
+          <t>Гарантийное удержание из оплаченных актов</t>
         </is>
       </c>
       <c r="B24" s="8">
-        <f>SUMIF('Встречное'!B6:B30,"иное",'Встречное'!D6:D30)</f>
-        <v/>
-      </c>
-      <c r="C24" s="4" t="inlineStr"/>
+        <f>SUMIF('Встречное'!B6:B30,"гарантийное удержание из оплаченных актов",'Встречное'!D6:D30)</f>
+        <v/>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>ваши деньги у генподрядчика. Проверьте по договору, наступил ли срок возврата</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
+          <t>Иное</t>
+        </is>
+      </c>
+      <c r="B25" s="8">
+        <f>SUMIF('Встречное'!B6:B30,"иное",'Встречное'!D6:D30)</f>
+        <v/>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>Задолженность по принятым и не оплаченным работам</t>
         </is>
       </c>
-      <c r="B25" s="8">
+      <c r="B26" s="8">
         <f>B14</f>
         <v/>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>из блока «Принято работ»</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Итого заявляется против возврата</t>
         </is>
       </c>
-      <c r="B26" s="23">
-        <f>ROUND(SUM(B20:B25),2)</f>
-        <v/>
-      </c>
-      <c r="C26" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="B27" s="23">
+        <f>ROUND(SUM(B20:B26),2)</f>
+        <v/>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Итог</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Требуют вернуть</t>
         </is>
       </c>
-      <c r="B29" s="8">
+      <c r="B30" s="8">
         <f>'Договор и аванс'!B11</f>
         <v/>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>из требования</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>Бесспорно к возврату</t>
-        </is>
-      </c>
-      <c r="B30" s="23">
-        <f>B17</f>
-        <v/>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>с этой суммы начинается разговор</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
+          <t>Не закрыто двусторонними актами</t>
+        </is>
+      </c>
+      <c r="B31" s="23">
+        <f>B17</f>
+        <v/>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>с этой суммы начинается разговор. Что из неё подлежит возврату — вопрос основания прекращения договора и его условий, не арифметики</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
           <t>Сальдо с учётом заявленного встречного</t>
         </is>
       </c>
-      <c r="B31" s="23">
-        <f>ROUND(B17-B26,2)</f>
-        <v/>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="B32" s="23">
+        <f>ROUND(B17-B27,2)</f>
+        <v/>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>положительное — к возврату, отрицательное — в вашу пользу. Это ваша позиция, а не результат: встречное надо обосновать документами</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Направление сальдо</t>
-        </is>
-      </c>
-      <c r="B32" s="24">
-        <f>IF(B31&gt;0,"к возврату генподрядчику",IF(B31&lt;0,"в вашу пользу","ноль"))</f>
-        <v/>
-      </c>
-      <c r="C32" s="4" t="inlineStr"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Расхождение между требованием и бесспорной частью</t>
-        </is>
-      </c>
-      <c r="B33" s="8">
-        <f>ROUND(B29-B30,2)</f>
-        <v/>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>ровно эта сумма требуется с вас сверх бесспорного. Она и есть предмет вашего ответа</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+          <t>Направление сальдо</t>
+        </is>
+      </c>
+      <c r="B33" s="24">
+        <f>IF(B32&gt;0,"к возврату генподрядчику",IF(B32&lt;0,"в вашу пользу","ноль"))</f>
+        <v/>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Расхождение между требованием и незакрытой частью</t>
+        </is>
+      </c>
+      <c r="B34" s="8">
+        <f>ROUND(B30-B31,2)</f>
+        <v/>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>ровно эта сумма требуется с вас сверх незакрытого актами. Она и есть предмет вашего ответа</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Проверки</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Сальдо сходится двумя способами</t>
-        </is>
-      </c>
-      <c r="B36" s="25">
-        <f>IF(ROUND(B11-B8,2)=ROUND(B14-B17,2),"сходится","ПРОВЕРЬТЕ: деньги приходили под акты, которые не подписаны обеими сторонами — расхождение "&amp;ROUND((B11-B8)-(B14-B17),2))</f>
-        <v/>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>обороты (принято минус поступило) сверяются с расчётом от аванса. Расхождение — не поломка, а находка: платёж лёг на неподписанный акт</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Ошибки в реестре «Выполнено»</t>
+          <t>Сальдо сходится двумя способами</t>
         </is>
       </c>
       <c r="B37" s="25">
-        <f>IF(COUNTIF('Выполнено'!L6:L45,"ОШИБКА*")=0,"нет","ПРОВЕРЬТЕ: строк с ошибкой — "&amp;COUNTIF('Выполнено'!L6:L45,"ОШИБКА*"))</f>
+        <f>IF(ROUND(B11-B8,2)=ROUND(B14-B17,2),"сходится","ПРОВЕРЬТЕ: деньги приходили под акты, которые не подписаны обеими сторонами — расхождение "&amp;ROUND((B11-B8)-(B14-B17),2))</f>
         <v/>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>колонка «Проверка» на листе «Выполнено»</t>
+          <t>обороты (принято минус поступило) сверяются с расчётом от аванса. Расхождение — не поломка, а находка: платёж лёг на неподписанный акт</t>
         </is>
       </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Ошибки в реестре «Встречное»</t>
+          <t>Ошибки в реестре «Выполнено»</t>
         </is>
       </c>
       <c r="B38" s="25">
-        <f>IF(COUNTIF('Встречное'!G6:G30,"ОШИБКА*")=0,"нет","ПРОВЕРЬТЕ: сумм без подтверждающего документа — "&amp;COUNTIF('Встречное'!G6:G30,"ОШИБКА*"))</f>
+        <f>IF(COUNTIF('Выполнено'!L6:L45,"ОШИБКА*")=0,"нет","ПРОВЕРЬТЕ: строк с ошибкой — "&amp;COUNTIF('Выполнено'!L6:L45,"ОШИБКА*"))</f>
         <v/>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>сумма без документа в письме работает против вас</t>
+          <t>колонка «Проверка» на листе «Выполнено»</t>
         </is>
       </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Заполнение листа «Договор и аванс»</t>
+          <t>Ошибки в реестре «Встречное»</t>
         </is>
       </c>
       <c r="B39" s="25">
-        <f>'Договор и аванс'!B19</f>
-        <v/>
-      </c>
-      <c r="C39" s="4" t="inlineStr"/>
+        <f>IF(COUNTIF('Встречное'!G6:G30,"ОШИБКА*")=0,"нет","ПРОВЕРЬТЕ: сумм без подтверждающего документа — "&amp;COUNTIF('Встречное'!G6:G30,"ОШИБКА*"))</f>
+        <v/>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>сумма без документа в письме работает против вас</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Требование больше полученного аванса</t>
+          <t>Заполнение листа «Договор и аванс»</t>
         </is>
       </c>
       <c r="B40" s="25">
-        <f>IF(B29&gt;B6+0.01,"ПРОВЕРЬТЕ: требуют больше, чем было получено авансом","нет")</f>
-        <v/>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>типовая ошибка второй стороны: в требование попадают суммы, авансом не являющиеся</t>
-        </is>
-      </c>
+        <f>'Договор и аванс'!B19</f>
+        <v/>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
+          <t>Требование больше полученного аванса</t>
+        </is>
+      </c>
+      <c r="B41" s="25">
+        <f>IF(B30&gt;B6+0.01,"ПРОВЕРЬТЕ: требуют больше, чем было получено авансом","нет")</f>
+        <v/>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>типовая ошибка второй стороны: в требование попадают суммы, авансом не являющиеся</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
           <t>Есть акты, переданные без подтверждения передачи</t>
         </is>
       </c>
-      <c r="B41" s="25">
+      <c r="B42" s="25">
         <f>IF(COUNTIFS('Выполнено'!F6:F45,"передан, не подписан",'Выполнено'!H6:H45,"")=0,"нет","ПРОВЕРЬТЕ: неподписанных актов без доказательства передачи — "&amp;COUNTIFS('Выполнено'!F6:F45,"передан, не подписан",'Выполнено'!H6:H45,""))</f>
         <v/>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>такой акт в переписке не работает: передача доказывается описью, отчётом об отслеживании, входящим штампом</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="46" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="44" ht="46" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Сальдо — это ваша позиция, посчитанная по вашим документам, а не решение по спору. Вторая сторона посчитает своё, и разница между двумя расчётами и есть то, о чём пойдёт разговор. Ценность этого листа в том, что ваша цифра появляется раньше и опирается на перечень документов, а не на слова.</t>
         </is>
@@ -3213,13 +3251,13 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3672,7 +3710,7 @@
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Неотработанный аванс по бесспорным документам</t>
+          <t>Аванс, не закрытый двусторонними актами</t>
         </is>
       </c>
       <c r="B20" s="32" t="inlineStr">
@@ -3720,7 +3758,7 @@
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Расхождение между требованием и бесспорной частью</t>
+          <t>Расхождение между требованием и незакрытой частью</t>
         </is>
       </c>
       <c r="B24" s="32" t="inlineStr">
